--- a/config/excel/card.xlsx
+++ b/config/excel/card.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20371"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3DEB031-B592-4224-A9AE-CA604A268CEA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0CFFFAA-445D-439D-8F77-76679093DC68}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="88">
   <si>
     <t>名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -307,6 +307,70 @@
   </si>
   <si>
     <t>攻击力+5，射程+6%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Hourglass_01_Silver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stat_Power_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Clock_01_Silver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Economy_Heart_Red.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI_ETC_Target_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI_ETC_Target_02_Brown</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stat_MoveSpeed_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gear_Bow_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gear_Helmet_03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI_Common_Speed_01_Yellow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI_Play_Skull_04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Economy_Energy_02_Blue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Material_Ore_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Misc_Fist_01_Gold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Horn_01_Wood</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Artifact_01_Gold</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -639,7 +703,7 @@
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="43.6640625" style="1" customWidth="1"/>
     <col min="3" max="4" width="8.88671875" style="1"/>
     <col min="5" max="5" width="41.109375" style="1" customWidth="1"/>
     <col min="6" max="6" width="15.44140625" style="1" customWidth="1"/>
@@ -680,6 +744,9 @@
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
@@ -700,6 +767,9 @@
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="B3" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
@@ -720,6 +790,9 @@
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B4" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
@@ -740,6 +813,9 @@
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="B5" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
@@ -759,6 +835,9 @@
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -780,6 +859,9 @@
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="B7" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
@@ -800,6 +882,9 @@
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="B8" s="1" t="s">
+        <v>78</v>
+      </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -820,6 +905,9 @@
       <c r="A9" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="B9" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="C9" s="1" t="s">
         <v>2</v>
       </c>
@@ -840,6 +928,9 @@
       <c r="A10" s="1" t="s">
         <v>53</v>
       </c>
+      <c r="B10" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="C10" s="1" t="s">
         <v>54</v>
       </c>
@@ -860,6 +951,9 @@
       <c r="A11" s="1" t="s">
         <v>57</v>
       </c>
+      <c r="B11" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="C11" s="1" t="s">
         <v>5</v>
       </c>
@@ -880,6 +974,9 @@
       <c r="A12" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="B12" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="C12" s="1" t="s">
         <v>5</v>
       </c>
@@ -900,6 +997,9 @@
       <c r="A13" s="1" t="s">
         <v>59</v>
       </c>
+      <c r="B13" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="C13" s="1" t="s">
         <v>5</v>
       </c>
@@ -920,6 +1020,9 @@
       <c r="A14" s="1" t="s">
         <v>60</v>
       </c>
+      <c r="B14" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="C14" s="1" t="s">
         <v>5</v>
       </c>
@@ -940,6 +1043,9 @@
       <c r="A15" s="1" t="s">
         <v>68</v>
       </c>
+      <c r="B15" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="C15" s="1" t="s">
         <v>5</v>
       </c>
@@ -960,6 +1066,9 @@
       <c r="A16" s="1" t="s">
         <v>32</v>
       </c>
+      <c r="B16" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="C16" s="1" t="s">
         <v>4</v>
       </c>
@@ -983,6 +1092,9 @@
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="B17" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="C17" s="1" t="s">
         <v>4</v>
       </c>
@@ -1006,6 +1118,9 @@
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
+      <c r="B18" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="C18" s="1" t="s">
         <v>4</v>
       </c>
@@ -1029,6 +1144,9 @@
       <c r="A19" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="B19" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="C19" s="1" t="s">
         <v>4</v>
       </c>
@@ -1052,6 +1170,9 @@
       <c r="A20" s="1" t="s">
         <v>38</v>
       </c>
+      <c r="B20" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="C20" s="1" t="s">
         <v>4</v>
       </c>
@@ -1074,6 +1195,9 @@
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>46</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>47</v>
